--- a/Team-Data/2013-14/4-13-2013-14.xlsx
+++ b/Team-Data/2013-14/4-13-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -763,13 +830,13 @@
         <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
         <v>19</v>
@@ -796,7 +863,7 @@
         <v>26</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>25</v>
@@ -805,7 +872,7 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>20</v>
@@ -814,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -921,22 +988,22 @@
         <v>-4.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>10</v>
@@ -975,7 +1042,7 @@
         <v>23</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.544</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1052,10 +1119,10 @@
         <v>8.6</v>
       </c>
       <c r="M4" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
         <v>18.4</v>
@@ -1067,31 +1134,31 @@
         <v>0.754</v>
       </c>
       <c r="R4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
         <v>20.7</v>
@@ -1100,10 +1167,10 @@
         <v>98.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1127,7 +1194,7 @@
         <v>10</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM4" t="n">
         <v>10</v>
@@ -1160,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1178,7 +1245,7 @@
         <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1297,7 +1364,7 @@
         <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
         <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.588</v>
+        <v>0.595</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J6" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.432</v>
@@ -1416,16 +1483,16 @@
         <v>6.2</v>
       </c>
       <c r="M6" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
         <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.78</v>
@@ -1437,19 +1504,19 @@
         <v>32.7</v>
       </c>
       <c r="T6" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U6" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V6" t="n">
         <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>6</v>
@@ -1464,19 +1531,19 @@
         <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
@@ -1536,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1791,7 @@
         <v>22</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2034,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>11</v>
@@ -2055,7 +2122,7 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>7</v>
@@ -2079,7 +2146,7 @@
         <v>26</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="H10" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
         <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="K10" t="n">
         <v>0.446</v>
@@ -2147,25 +2214,25 @@
         <v>19.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
         <v>0.671</v>
       </c>
       <c r="R10" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U10" t="n">
         <v>20.9</v>
@@ -2177,25 +2244,25 @@
         <v>8.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y10" t="n">
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB10" t="n">
         <v>100.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2228,7 +2295,7 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2243,7 +2310,7 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2258,13 +2325,13 @@
         <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -2299,40 +2366,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
         <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>0.613</v>
+        <v>0.62</v>
       </c>
       <c r="H11" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J11" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.461</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="O11" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P11" t="n">
         <v>21</v>
@@ -2341,13 +2408,13 @@
         <v>0.755</v>
       </c>
       <c r="R11" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S11" t="n">
         <v>34.4</v>
       </c>
       <c r="T11" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U11" t="n">
         <v>23.2</v>
@@ -2359,25 +2426,25 @@
         <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
         <v>4.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA11" t="n">
         <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC11" t="n">
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,25 +2456,25 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>9</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
         <v>26</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>14</v>
@@ -2604,7 +2671,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>4</v>
@@ -2616,7 +2683,7 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -2663,40 +2730,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
         <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H13" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I13" t="n">
         <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K13" t="n">
         <v>0.448</v>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O13" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P13" t="n">
         <v>23.4</v>
@@ -2714,13 +2781,13 @@
         <v>44.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X13" t="n">
         <v>5.5</v>
@@ -2735,13 +2802,13 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2762,22 +2829,22 @@
         <v>28</v>
       </c>
       <c r="AK13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM13" t="n">
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>8</v>
@@ -2813,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>14</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>0.313</v>
+        <v>0.316</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J15" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.448</v>
@@ -3054,28 +3121,28 @@
         <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.38</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P15" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U15" t="n">
         <v>24.3</v>
@@ -3084,7 +3151,7 @@
         <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
         <v>5.5</v>
@@ -3093,19 +3160,19 @@
         <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.6</v>
+        <v>102.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3123,13 +3190,13 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3138,7 +3205,7 @@
         <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3153,13 +3220,13 @@
         <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU15" t="n">
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3168,13 +3235,13 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" t="n">
         <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.463</v>
@@ -3239,28 +3306,28 @@
         <v>13.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R16" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S16" t="n">
         <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
         <v>13.6</v>
@@ -3269,25 +3336,25 @@
         <v>7.7</v>
       </c>
       <c r="X16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y16" t="n">
         <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA16" t="n">
         <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3305,10 +3372,10 @@
         <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3335,10 +3402,10 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3347,13 +3414,13 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
         <v>11</v>
@@ -3499,7 +3566,7 @@
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>26</v>
@@ -3687,7 +3754,7 @@
         <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
         <v>21</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3822,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J19" t="n">
         <v>87.5</v>
@@ -3791,34 +3858,34 @@
         <v>21.5</v>
       </c>
       <c r="P19" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
         <v>12.5</v>
       </c>
       <c r="S19" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
         <v>44.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V19" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>3.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z19" t="n">
         <v>18.3</v>
@@ -3830,28 +3897,28 @@
         <v>106.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>17</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI19" t="n">
         <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
@@ -3878,16 +3945,16 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4027,7 +4094,7 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
         <v>17</v>
@@ -4069,7 +4136,7 @@
         <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F21" t="n">
         <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>0.438</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4158,16 +4225,16 @@
         <v>20.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
         <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
         <v>20.2</v>
@@ -4179,13 +4246,13 @@
         <v>7.6</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
         <v>19.6</v>
@@ -4194,10 +4261,10 @@
         <v>98.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="n">
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.725</v>
+        <v>0.734</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4322,16 +4389,16 @@
         <v>82.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
         <v>8.1</v>
       </c>
       <c r="M22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O22" t="n">
         <v>20.1</v>
@@ -4340,28 +4407,28 @@
         <v>24.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="R22" t="n">
         <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T22" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U22" t="n">
         <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
         <v>3.6</v>
@@ -4373,13 +4440,13 @@
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
         <v>15</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4424,19 +4491,19 @@
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
         <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
@@ -4501,7 +4568,7 @@
         <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
         <v>0.445</v>
@@ -4513,37 +4580,37 @@
         <v>19.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
         <v>21.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>5.5</v>
@@ -4555,19 +4622,19 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC23" t="n">
         <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
         <v>28</v>
@@ -4606,10 +4673,10 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
@@ -4618,10 +4685,10 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY23" t="n">
         <v>22</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4794,7 +4861,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4946,10 +5013,10 @@
         <v>12</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4964,7 +5031,7 @@
         <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -5029,52 +5096,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654</v>
+        <v>0.65</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J26" t="n">
         <v>86.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S26" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T26" t="n">
         <v>46.2</v>
@@ -5092,25 +5159,25 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.7</v>
+        <v>106.6</v>
       </c>
       <c r="AC26" t="n">
         <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>7</v>
@@ -5122,7 +5189,7 @@
         <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
         <v>4</v>
@@ -5131,7 +5198,7 @@
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
@@ -5143,13 +5210,13 @@
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5173,7 +5240,7 @@
         <v>6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" t="n">
         <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.346</v>
+        <v>0.338</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5247,28 +5314,28 @@
         <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R27" t="n">
         <v>12.1</v>
       </c>
       <c r="S27" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T27" t="n">
         <v>44.3</v>
       </c>
       <c r="U27" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V27" t="n">
         <v>15.2</v>
       </c>
       <c r="W27" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
@@ -5286,10 +5353,10 @@
         <v>100.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>22</v>
@@ -5310,7 +5377,7 @@
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>28</v>
@@ -5334,7 +5401,7 @@
         <v>5</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
@@ -5534,13 +5601,13 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
         <v>6</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -5575,22 +5642,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n">
         <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>0.588</v>
+        <v>0.582</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J29" t="n">
         <v>82</v>
@@ -5608,13 +5675,13 @@
         <v>0.372</v>
       </c>
       <c r="O29" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P29" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R29" t="n">
         <v>11.4</v>
@@ -5626,58 +5693,58 @@
         <v>42.4</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y29" t="n">
         <v>4.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
         <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>101.3</v>
+        <v>101.1</v>
       </c>
       <c r="AC29" t="n">
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
@@ -5692,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR29" t="n">
         <v>14</v>
@@ -5713,13 +5780,13 @@
         <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>27</v>
@@ -5859,7 +5926,7 @@
         <v>25</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>23</v>
@@ -5883,7 +5950,7 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6047,7 +6114,7 @@
         <v>19</v>
       </c>
       <c r="AN31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
         <v>28</v>
@@ -6077,7 +6144,7 @@
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-13-2013-14</t>
+          <t>2014-04-13</t>
         </is>
       </c>
     </row>
